--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -98,10 +98,10 @@
     <t>生肖·鸡</t>
   </si>
   <si>
+    <t>生肖·狗</t>
+  </si>
+  <si>
     <t>生肖·猪</t>
-  </si>
-  <si>
-    <t>生肖·狗</t>
   </si>
 </sst>
 </file>

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>5,10,10,5</t>
+  </si>
+  <si>
+    <t>10,10,10,10</t>
   </si>
   <si>
     <t>生肖·牛</t>
@@ -1185,7 +1188,7 @@
         <v>13</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1193,7 +1196,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -1208,7 +1211,7 @@
         <v>13</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1216,7 +1219,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -1231,7 +1234,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1239,7 +1242,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
@@ -1254,7 +1257,7 @@
         <v>13</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1262,7 +1265,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -1277,7 +1280,7 @@
         <v>13</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1285,7 +1288,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
@@ -1300,7 +1303,7 @@
         <v>13</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:9">
@@ -1308,7 +1311,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="1">
         <v>7</v>
@@ -1323,7 +1326,7 @@
         <v>13</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:9">
@@ -1331,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1">
         <v>8</v>
@@ -1346,7 +1349,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:9">
@@ -1354,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1">
         <v>9</v>
@@ -1369,7 +1372,7 @@
         <v>13</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:9">
@@ -1377,7 +1380,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
@@ -1392,7 +1395,7 @@
         <v>13</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:9">
@@ -1400,7 +1403,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16" s="1">
         <v>11</v>
@@ -1415,7 +1418,7 @@
         <v>13</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:22">
@@ -1423,7 +1426,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="1">
         <v>12</v>
@@ -1438,7 +1441,7 @@
         <v>13</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -50,6 +50,9 @@
     <t>AttchValueList</t>
   </si>
   <si>
+    <t>LayerValueList</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -72,6 +75,9 @@
   </si>
   <si>
     <t>10,10,10,10</t>
+  </si>
+  <si>
+    <t>1,10,10,10</t>
   </si>
   <si>
     <t>生肖·牛</t>
@@ -1074,26 +1080,28 @@
     <col min="5" max="5" width="14.5833333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.25" style="2" customWidth="1"/>
-    <col min="8" max="9" width="21.25" style="2" customWidth="1"/>
-    <col min="10" max="16369" width="9" style="2"/>
+    <col min="8" max="10" width="21.25" style="2" customWidth="1"/>
+    <col min="11" max="16369" width="9" style="2"/>
     <col min="16370" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1117,12 +1125,15 @@
       <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1142,38 +1153,44 @@
       <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1182,21 +1199,24 @@
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -1205,21 +1225,24 @@
         <v>1</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -1228,21 +1251,24 @@
         <v>1</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
@@ -1251,21 +1277,24 @@
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -1274,21 +1303,24 @@
         <v>1</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
@@ -1297,21 +1329,24 @@
         <v>1</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E12" s="1">
         <v>7</v>
@@ -1320,21 +1355,24 @@
         <v>1</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1">
         <v>8</v>
@@ -1343,21 +1381,24 @@
         <v>1</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E14" s="1">
         <v>9</v>
@@ -1366,21 +1407,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
@@ -1389,21 +1433,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:9">
+        <v>15</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E16" s="1">
         <v>11</v>
@@ -1412,13 +1459,16 @@
         <v>1</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:22">
@@ -1426,7 +1476,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E17" s="1">
         <v>12</v>
@@ -1435,13 +1485,16 @@
         <v>1</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -1462,20 +1515,23 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="20" customHeight="1" spans="7:9">
+    <row r="20" customHeight="1" spans="7:10">
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="7:9">
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" customHeight="1" spans="7:10">
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" customHeight="1" spans="7:22">
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -1489,6 +1545,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -1498,39 +1555,45 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="27" customHeight="1" spans="7:9">
+    <row r="27" customHeight="1" spans="7:10">
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="7:9">
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="7:10">
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="7:9">
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" customHeight="1" spans="7:10">
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="7:9">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" customHeight="1" spans="7:10">
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="7:9">
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="7:10">
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="7:9">
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="7:10">
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3 J4 J5 C3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -111,6 +111,42 @@
   </si>
   <si>
     <t>生肖·猪</t>
+  </si>
+  <si>
+    <t>水瓶座</t>
+  </si>
+  <si>
+    <t>双鱼座</t>
+  </si>
+  <si>
+    <t>白羊座</t>
+  </si>
+  <si>
+    <t>金牛座</t>
+  </si>
+  <si>
+    <t>双子座</t>
+  </si>
+  <si>
+    <t>巨蟹座</t>
+  </si>
+  <si>
+    <t>狮子座</t>
+  </si>
+  <si>
+    <t>处女座</t>
+  </si>
+  <si>
+    <t>天秤座</t>
+  </si>
+  <si>
+    <t>天蝎座</t>
+  </si>
+  <si>
+    <t>射手座</t>
+  </si>
+  <si>
+    <t>摩羯座</t>
   </si>
 </sst>
 </file>
@@ -123,7 +159,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +177,12 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -613,143 +655,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1185,7 +1228,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1198,20 +1241,20 @@
       <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="G6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1224,20 +1267,20 @@
       <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="G7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1250,20 +1293,20 @@
       <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="G8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1276,20 +1319,20 @@
       <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="G9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1302,20 +1345,20 @@
       <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="G10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1328,20 +1371,20 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:10">
+      <c r="G11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1354,20 +1397,20 @@
       <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:10">
+      <c r="G12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1380,20 +1423,20 @@
       <c r="F13" s="1">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:10">
+      <c r="G13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1406,20 +1449,20 @@
       <c r="F14" s="1">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:10">
+      <c r="G14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1432,20 +1475,20 @@
       <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:10">
+      <c r="G15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1458,16 +1501,16 @@
       <c r="F16" s="1">
         <v>1</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="4" t="s">
+      <c r="G16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1484,16 +1527,16 @@
       <c r="F17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="4" t="s">
+      <c r="G17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="O17" s="1"/>
@@ -1505,7 +1548,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" customHeight="1" spans="15:22">
+    <row r="18" customHeight="1" spans="3:22">
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -1515,23 +1558,109 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="20" customHeight="1" spans="7:10">
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="7:10">
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" spans="7:22">
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
+    <row r="19" customHeight="1" spans="3:22">
+      <c r="C19" s="1">
+        <v>13</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="1">
+        <v>13</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:22">
+      <c r="C20" s="1">
+        <v>14</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="1">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:22">
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="1">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:22">
+      <c r="C22" s="1">
+        <v>16</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="1">
+        <v>16</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -1541,11 +1670,31 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" customHeight="1" spans="7:22">
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+    <row r="23" customHeight="1" spans="3:22">
+      <c r="C23" s="1">
+        <v>17</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="1">
+        <v>17</v>
+      </c>
+      <c r="F23" s="1">
+        <v>2</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -1555,37 +1704,195 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="27" customHeight="1" spans="7:10">
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="7:10">
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="7:10">
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="7:10">
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="7:10">
+    <row r="24" customHeight="1" spans="3:22">
+      <c r="C24" s="1">
+        <v>18</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="1">
+        <v>18</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:22">
+      <c r="C25" s="1">
+        <v>19</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="1">
+        <v>19</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:22">
+      <c r="C26" s="1">
+        <v>20</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="1">
+        <v>20</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:22">
+      <c r="C27" s="1">
+        <v>21</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="1">
+        <v>21</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:22">
+      <c r="C28" s="1">
+        <v>22</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="1">
+        <v>22</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:22">
+      <c r="C29" s="1">
+        <v>23</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="1">
+        <v>23</v>
+      </c>
+      <c r="F29" s="1">
+        <v>2</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:22">
+      <c r="C30" s="1">
+        <v>24</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="1">
+        <v>24</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:22">
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" customHeight="1" spans="7:10">
+    <row r="32" customHeight="1" spans="3:22">
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1593,7 +1900,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3 J4 J5 C3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>水瓶座</t>
+  </si>
+  <si>
+    <t>15,15,15,15</t>
   </si>
   <si>
     <t>双鱼座</t>
@@ -1578,7 +1581,7 @@
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>16</v>
@@ -1589,7 +1592,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1">
         <v>14</v>
@@ -1604,7 +1607,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>16</v>
@@ -1615,7 +1618,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1">
         <v>15</v>
@@ -1630,7 +1633,7 @@
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>16</v>
@@ -1641,7 +1644,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" s="1">
         <v>16</v>
@@ -1656,7 +1659,7 @@
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>16</v>
@@ -1675,7 +1678,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="1">
         <v>17</v>
@@ -1690,7 +1693,7 @@
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>16</v>
@@ -1709,7 +1712,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24" s="1">
         <v>18</v>
@@ -1724,7 +1727,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>16</v>
@@ -1735,7 +1738,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E25" s="1">
         <v>19</v>
@@ -1750,7 +1753,7 @@
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>16</v>
@@ -1761,7 +1764,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E26" s="1">
         <v>20</v>
@@ -1776,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>16</v>
@@ -1787,7 +1790,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E27" s="1">
         <v>21</v>
@@ -1802,7 +1805,7 @@
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>16</v>
@@ -1813,7 +1816,7 @@
         <v>22</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E28" s="1">
         <v>22</v>
@@ -1828,7 +1831,7 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>16</v>
@@ -1839,7 +1842,7 @@
         <v>23</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E29" s="1">
         <v>23</v>
@@ -1854,7 +1857,7 @@
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>16</v>
@@ -1865,7 +1868,7 @@
         <v>24</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E30" s="1">
         <v>24</v>
@@ -1880,7 +1883,7 @@
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>16</v>

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>15,15,15,15</t>
+  </si>
+  <si>
+    <t>1,15,15,15</t>
   </si>
   <si>
     <t>双鱼座</t>
@@ -1584,7 +1587,7 @@
         <v>29</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:22">
@@ -1592,7 +1595,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" s="1">
         <v>14</v>
@@ -1610,7 +1613,7 @@
         <v>29</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:22">
@@ -1618,7 +1621,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" s="1">
         <v>15</v>
@@ -1636,7 +1639,7 @@
         <v>29</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:22">
@@ -1644,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="1">
         <v>16</v>
@@ -1662,7 +1665,7 @@
         <v>29</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -1678,7 +1681,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E23" s="1">
         <v>17</v>
@@ -1696,7 +1699,7 @@
         <v>29</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -1712,7 +1715,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24" s="1">
         <v>18</v>
@@ -1730,7 +1733,7 @@
         <v>29</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:22">
@@ -1738,7 +1741,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E25" s="1">
         <v>19</v>
@@ -1756,7 +1759,7 @@
         <v>29</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:22">
@@ -1764,7 +1767,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E26" s="1">
         <v>20</v>
@@ -1782,7 +1785,7 @@
         <v>29</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:22">
@@ -1790,7 +1793,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E27" s="1">
         <v>21</v>
@@ -1808,7 +1811,7 @@
         <v>29</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:22">
@@ -1816,7 +1819,7 @@
         <v>22</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E28" s="1">
         <v>22</v>
@@ -1834,7 +1837,7 @@
         <v>29</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:22">
@@ -1842,7 +1845,7 @@
         <v>23</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E29" s="1">
         <v>23</v>
@@ -1860,7 +1863,7 @@
         <v>29</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:22">
@@ -1868,7 +1871,7 @@
         <v>24</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E30" s="1">
         <v>24</v>
@@ -1886,7 +1889,7 @@
         <v>29</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:22">

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>Cycle</t>
+  </si>
+  <si>
+    <t>Required</t>
   </si>
   <si>
     <t>AttrIdList</t>
@@ -1119,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1127,30 +1130,30 @@
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.1666666666667" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.5833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.25" style="2" customWidth="1"/>
-    <col min="8" max="10" width="21.25" style="2" customWidth="1"/>
-    <col min="11" max="16369" width="9" style="2"/>
-    <col min="16370" max="16384" width="9" style="1"/>
+    <col min="6" max="7" width="9.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.25" style="2" customWidth="1"/>
+    <col min="9" max="11" width="21.25" style="2" customWidth="1"/>
+    <col min="12" max="16370" width="9" style="2"/>
+    <col min="16371" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1177,12 +1180,15 @@
       <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1205,41 +1211,47 @@
       <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
+        <v>12</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1247,8 +1259,8 @@
       <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>13</v>
+      <c r="G6" s="1">
+        <v>10</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>14</v>
@@ -1259,13 +1271,16 @@
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K6" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -1273,8 +1288,8 @@
       <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>13</v>
+      <c r="G7" s="1">
+        <v>10</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>14</v>
@@ -1285,13 +1300,16 @@
       <c r="J7" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -1299,8 +1317,8 @@
       <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>13</v>
+      <c r="G8" s="1">
+        <v>10</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>14</v>
@@ -1311,13 +1329,16 @@
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K8" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
@@ -1325,8 +1346,8 @@
       <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>13</v>
+      <c r="G9" s="1">
+        <v>10</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>14</v>
@@ -1337,13 +1358,16 @@
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K9" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -1351,8 +1375,8 @@
       <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>13</v>
+      <c r="G10" s="1">
+        <v>10</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>14</v>
@@ -1363,13 +1387,16 @@
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K10" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
@@ -1377,8 +1404,8 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>13</v>
+      <c r="G11" s="1">
+        <v>10</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>14</v>
@@ -1389,13 +1416,16 @@
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:10">
+      <c r="K11" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:11">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1">
         <v>7</v>
@@ -1403,8 +1433,8 @@
       <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>13</v>
+      <c r="G12" s="1">
+        <v>10</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>14</v>
@@ -1415,13 +1445,16 @@
       <c r="J12" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:10">
+      <c r="K12" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:11">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="1">
         <v>8</v>
@@ -1429,8 +1462,8 @@
       <c r="F13" s="1">
         <v>1</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>13</v>
+      <c r="G13" s="1">
+        <v>10</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>14</v>
@@ -1441,13 +1474,16 @@
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:10">
+      <c r="K13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:11">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1">
         <v>9</v>
@@ -1455,8 +1491,8 @@
       <c r="F14" s="1">
         <v>1</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>13</v>
+      <c r="G14" s="1">
+        <v>10</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>14</v>
@@ -1467,13 +1503,16 @@
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:10">
+      <c r="K14" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:11">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
@@ -1481,8 +1520,8 @@
       <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>13</v>
+      <c r="G15" s="1">
+        <v>10</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>14</v>
@@ -1493,13 +1532,16 @@
       <c r="J15" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:10">
+      <c r="K15" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:11">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="1">
         <v>11</v>
@@ -1507,8 +1549,8 @@
       <c r="F16" s="1">
         <v>1</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>13</v>
+      <c r="G16" s="1">
+        <v>10</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>14</v>
@@ -1519,13 +1561,16 @@
       <c r="J16" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:22">
+      <c r="K16" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:23">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E17" s="1">
         <v>12</v>
@@ -1533,8 +1578,8 @@
       <c r="F17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>13</v>
+      <c r="G17" s="1">
+        <v>10</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>14</v>
@@ -1545,7 +1590,9 @@
       <c r="J17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="O17" s="1"/>
+      <c r="K17" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
@@ -1553,9 +1600,9 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="3:22">
-      <c r="O18" s="1"/>
+      <c r="W17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:23">
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -1563,13 +1610,14 @@
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="3:22">
+      <c r="W18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:23">
       <c r="C19" s="1">
         <v>13</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E19" s="1">
         <v>13</v>
@@ -1577,25 +1625,28 @@
       <c r="F19" s="1">
         <v>2</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>13</v>
+      <c r="G19" s="1">
+        <v>20</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:22">
+      <c r="K19" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:23">
       <c r="C20" s="1">
         <v>14</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" s="1">
         <v>14</v>
@@ -1603,25 +1654,28 @@
       <c r="F20" s="1">
         <v>2</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>13</v>
+      <c r="G20" s="1">
+        <v>20</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:22">
+      <c r="K20" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:23">
       <c r="C21" s="1">
         <v>15</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="1">
         <v>15</v>
@@ -1629,25 +1683,28 @@
       <c r="F21" s="1">
         <v>2</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>13</v>
+      <c r="G21" s="1">
+        <v>20</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:22">
+      <c r="K21" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:23">
       <c r="C22" s="1">
         <v>16</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22" s="1">
         <v>16</v>
@@ -1655,19 +1712,21 @@
       <c r="F22" s="1">
         <v>2</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>13</v>
+      <c r="G22" s="1">
+        <v>20</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="O22" s="1"/>
+      <c r="K22" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -1675,13 +1734,14 @@
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="3:22">
+      <c r="W22" s="1"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:23">
       <c r="C23" s="1">
         <v>17</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" s="1">
         <v>17</v>
@@ -1689,19 +1749,21 @@
       <c r="F23" s="1">
         <v>2</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>13</v>
+      <c r="G23" s="1">
+        <v>20</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="O23" s="1"/>
+      <c r="K23" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -1709,13 +1771,14 @@
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="3:22">
+      <c r="W23" s="1"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:23">
       <c r="C24" s="1">
         <v>18</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24" s="1">
         <v>18</v>
@@ -1723,25 +1786,28 @@
       <c r="F24" s="1">
         <v>2</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>13</v>
+      <c r="G24" s="1">
+        <v>20</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:22">
+      <c r="K24" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:23">
       <c r="C25" s="1">
         <v>19</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E25" s="1">
         <v>19</v>
@@ -1749,25 +1815,28 @@
       <c r="F25" s="1">
         <v>2</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>13</v>
+      <c r="G25" s="1">
+        <v>20</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:22">
+      <c r="K25" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:23">
       <c r="C26" s="1">
         <v>20</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E26" s="1">
         <v>20</v>
@@ -1775,25 +1844,28 @@
       <c r="F26" s="1">
         <v>2</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>13</v>
+      <c r="G26" s="1">
+        <v>20</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:22">
+      <c r="K26" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:23">
       <c r="C27" s="1">
         <v>21</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E27" s="1">
         <v>21</v>
@@ -1801,25 +1873,28 @@
       <c r="F27" s="1">
         <v>2</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>13</v>
+      <c r="G27" s="1">
+        <v>20</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:22">
+      <c r="K27" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:23">
       <c r="C28" s="1">
         <v>22</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E28" s="1">
         <v>22</v>
@@ -1827,25 +1902,28 @@
       <c r="F28" s="1">
         <v>2</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>13</v>
+      <c r="G28" s="1">
+        <v>20</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:22">
+      <c r="K28" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:23">
       <c r="C29" s="1">
         <v>23</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E29" s="1">
         <v>23</v>
@@ -1853,25 +1931,28 @@
       <c r="F29" s="1">
         <v>2</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>13</v>
+      <c r="G29" s="1">
+        <v>20</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:22">
+      <c r="K29" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:23">
       <c r="C30" s="1">
         <v>24</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E30" s="1">
         <v>24</v>
@@ -1879,34 +1960,37 @@
       <c r="F30" s="1">
         <v>2</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>13</v>
+      <c r="G30" s="1">
+        <v>20</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:22">
-      <c r="G31" s="1"/>
+      <c r="K30" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:23">
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:22">
-      <c r="G32" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:23">
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 G5 C3:F5 H3:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="58">
   <si>
     <t>ID</t>
   </si>
@@ -156,6 +156,51 @@
   </si>
   <si>
     <t>摩羯座</t>
+  </si>
+  <si>
+    <t>紫微星</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,2013</t>
+  </si>
+  <si>
+    <t>5,10,5,5</t>
+  </si>
+  <si>
+    <t>20,20,20,20</t>
+  </si>
+  <si>
+    <t>2,20,20,20</t>
+  </si>
+  <si>
+    <t>天机星</t>
+  </si>
+  <si>
+    <t>太阳星</t>
+  </si>
+  <si>
+    <t>太阴星</t>
+  </si>
+  <si>
+    <t>武曲星</t>
+  </si>
+  <si>
+    <t>巨门星</t>
+  </si>
+  <si>
+    <t>天相星</t>
+  </si>
+  <si>
+    <t>廉贞星</t>
+  </si>
+  <si>
+    <t>贪狼星</t>
+  </si>
+  <si>
+    <t>破军星</t>
+  </si>
+  <si>
+    <t>七杀星</t>
   </si>
 </sst>
 </file>
@@ -177,20 +222,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -794,7 +839,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -802,6 +847,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1122,7 +1170,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1262,16 +1310,16 @@
       <c r="G6" s="1">
         <v>10</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="H6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1291,16 +1339,16 @@
       <c r="G7" s="1">
         <v>10</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="H7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1320,16 +1368,16 @@
       <c r="G8" s="1">
         <v>10</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1349,16 +1397,16 @@
       <c r="G9" s="1">
         <v>10</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="H9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1378,16 +1426,16 @@
       <c r="G10" s="1">
         <v>10</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="H10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1407,16 +1455,16 @@
       <c r="G11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="H11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1436,16 +1484,16 @@
       <c r="G12" s="1">
         <v>10</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="H12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1465,16 +1513,16 @@
       <c r="G13" s="1">
         <v>10</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="5" t="s">
+      <c r="H13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1494,16 +1542,16 @@
       <c r="G14" s="1">
         <v>10</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="5" t="s">
+      <c r="H14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1523,16 +1571,16 @@
       <c r="G15" s="1">
         <v>10</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="5" t="s">
+      <c r="H15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1552,16 +1600,16 @@
       <c r="G16" s="1">
         <v>10</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="H16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1581,16 +1629,16 @@
       <c r="G17" s="1">
         <v>10</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="H17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="P17" s="1"/>
@@ -1628,16 +1676,16 @@
       <c r="G19" s="1">
         <v>20</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="5" t="s">
+      <c r="H19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1657,16 +1705,16 @@
       <c r="G20" s="1">
         <v>20</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K20" s="5" t="s">
+      <c r="H20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1686,16 +1734,16 @@
       <c r="G21" s="1">
         <v>20</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="5" t="s">
+      <c r="H21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1715,16 +1763,16 @@
       <c r="G22" s="1">
         <v>20</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K22" s="5" t="s">
+      <c r="H22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="6" t="s">
         <v>31</v>
       </c>
       <c r="P22" s="1"/>
@@ -1752,16 +1800,16 @@
       <c r="G23" s="1">
         <v>20</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="5" t="s">
+      <c r="H23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="6" t="s">
         <v>31</v>
       </c>
       <c r="P23" s="1"/>
@@ -1789,16 +1837,16 @@
       <c r="G24" s="1">
         <v>20</v>
       </c>
-      <c r="H24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K24" s="5" t="s">
+      <c r="H24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1818,16 +1866,16 @@
       <c r="G25" s="1">
         <v>20</v>
       </c>
-      <c r="H25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K25" s="5" t="s">
+      <c r="H25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1847,16 +1895,16 @@
       <c r="G26" s="1">
         <v>20</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K26" s="5" t="s">
+      <c r="H26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1876,16 +1924,16 @@
       <c r="G27" s="1">
         <v>20</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K27" s="5" t="s">
+      <c r="H27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1905,16 +1953,16 @@
       <c r="G28" s="1">
         <v>20</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K28" s="5" t="s">
+      <c r="H28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1934,16 +1982,16 @@
       <c r="G29" s="1">
         <v>20</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" s="5" t="s">
+      <c r="H29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1963,16 +2011,16 @@
       <c r="G30" s="1">
         <v>20</v>
       </c>
-      <c r="H30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K30" s="5" t="s">
+      <c r="H30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1983,14 +2031,356 @@
       <c r="K31" s="1"/>
     </row>
     <row r="32" customHeight="1" spans="3:23">
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
+      <c r="C32" s="1">
+        <v>25</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="1">
+        <v>25</v>
+      </c>
+      <c r="F32" s="1">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1">
+        <v>30</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:11">
+      <c r="C33" s="1">
+        <v>26</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="1">
+        <v>26</v>
+      </c>
+      <c r="F33" s="1">
+        <v>3</v>
+      </c>
+      <c r="G33" s="1">
+        <v>30</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:11">
+      <c r="C34" s="1">
+        <v>27</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="1">
+        <v>27</v>
+      </c>
+      <c r="F34" s="1">
+        <v>3</v>
+      </c>
+      <c r="G34" s="1">
+        <v>30</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:11">
+      <c r="C35" s="1">
+        <v>28</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="1">
+        <v>28</v>
+      </c>
+      <c r="F35" s="1">
+        <v>3</v>
+      </c>
+      <c r="G35" s="1">
+        <v>30</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:11">
+      <c r="C36" s="1">
+        <v>29</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="1">
+        <v>29</v>
+      </c>
+      <c r="F36" s="1">
+        <v>3</v>
+      </c>
+      <c r="G36" s="1">
+        <v>30</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:11">
+      <c r="C37" s="1">
+        <v>30</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="1">
+        <v>30</v>
+      </c>
+      <c r="F37" s="1">
+        <v>3</v>
+      </c>
+      <c r="G37" s="1">
+        <v>30</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:11">
+      <c r="C38" s="1">
+        <v>31</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E38" s="1">
+        <v>31</v>
+      </c>
+      <c r="F38" s="1">
+        <v>3</v>
+      </c>
+      <c r="G38" s="1">
+        <v>30</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:11">
+      <c r="C39" s="1">
+        <v>32</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="1">
+        <v>32</v>
+      </c>
+      <c r="F39" s="1">
+        <v>3</v>
+      </c>
+      <c r="G39" s="1">
+        <v>30</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:11">
+      <c r="C40" s="1">
+        <v>33</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="1">
+        <v>33</v>
+      </c>
+      <c r="F40" s="1">
+        <v>3</v>
+      </c>
+      <c r="G40" s="1">
+        <v>30</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:11">
+      <c r="C41" s="1">
+        <v>34</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="1">
+        <v>34</v>
+      </c>
+      <c r="F41" s="1">
+        <v>3</v>
+      </c>
+      <c r="G41" s="1">
+        <v>30</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:11">
+      <c r="C42" s="1">
+        <v>35</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="1">
+        <v>35</v>
+      </c>
+      <c r="F42" s="1">
+        <v>3</v>
+      </c>
+      <c r="G42" s="1">
+        <v>30</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:11">
+      <c r="C43" s="1">
+        <v>36</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="1">
+        <v>36</v>
+      </c>
+      <c r="F43" s="1">
+        <v>3</v>
+      </c>
+      <c r="G43" s="1">
+        <v>30</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 G5 C3:F5 H3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -161,7 +161,7 @@
     <t>紫微星</t>
   </si>
   <si>
-    <t>2001,2003,2010,2013</t>
+    <t>2001,2012,2003,2013</t>
   </si>
   <si>
     <t>5,10,5,5</t>
@@ -2044,7 +2044,7 @@
         <v>3</v>
       </c>
       <c r="G32" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>44</v>
@@ -2073,7 +2073,7 @@
         <v>3</v>
       </c>
       <c r="G33" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>44</v>
@@ -2102,7 +2102,7 @@
         <v>3</v>
       </c>
       <c r="G34" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>44</v>
@@ -2131,7 +2131,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>44</v>
@@ -2160,7 +2160,7 @@
         <v>3</v>
       </c>
       <c r="G36" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>44</v>
@@ -2189,7 +2189,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>44</v>
@@ -2218,7 +2218,7 @@
         <v>3</v>
       </c>
       <c r="G38" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>44</v>
@@ -2247,7 +2247,7 @@
         <v>3</v>
       </c>
       <c r="G39" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>44</v>
@@ -2276,7 +2276,7 @@
         <v>3</v>
       </c>
       <c r="G40" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>44</v>
@@ -2305,7 +2305,7 @@
         <v>3</v>
       </c>
       <c r="G41" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>44</v>
@@ -2334,7 +2334,7 @@
         <v>3</v>
       </c>
       <c r="G42" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>44</v>
@@ -2363,7 +2363,7 @@
         <v>3</v>
       </c>
       <c r="G43" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>44</v>

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="57">
   <si>
     <t>ID</t>
   </si>
@@ -162,9 +167,6 @@
   </si>
   <si>
     <t>2001,2012,2003,2013</t>
-  </si>
-  <si>
-    <t>5,10,5,5</t>
   </si>
   <si>
     <t>20,20,20,20</t>
@@ -2050,13 +2052,13 @@
         <v>44</v>
       </c>
       <c r="I32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="K32" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:11">
@@ -2064,7 +2066,7 @@
         <v>26</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33" s="1">
         <v>26</v>
@@ -2079,13 +2081,13 @@
         <v>44</v>
       </c>
       <c r="I33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="K33" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:11">
@@ -2093,7 +2095,7 @@
         <v>27</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" s="1">
         <v>27</v>
@@ -2108,13 +2110,13 @@
         <v>44</v>
       </c>
       <c r="I34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="6" t="s">
+      <c r="K34" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:11">
@@ -2122,7 +2124,7 @@
         <v>28</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E35" s="1">
         <v>28</v>
@@ -2137,13 +2139,13 @@
         <v>44</v>
       </c>
       <c r="I35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="K35" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:11">
@@ -2151,7 +2153,7 @@
         <v>29</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E36" s="1">
         <v>29</v>
@@ -2166,13 +2168,13 @@
         <v>44</v>
       </c>
       <c r="I36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J36" s="6" t="s">
+      <c r="K36" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:11">
@@ -2180,7 +2182,7 @@
         <v>30</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E37" s="1">
         <v>30</v>
@@ -2195,13 +2197,13 @@
         <v>44</v>
       </c>
       <c r="I37" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J37" s="6" t="s">
+      <c r="K37" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:11">
@@ -2209,7 +2211,7 @@
         <v>31</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E38" s="1">
         <v>31</v>
@@ -2224,13 +2226,13 @@
         <v>44</v>
       </c>
       <c r="I38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J38" s="6" t="s">
+      <c r="K38" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:11">
@@ -2238,7 +2240,7 @@
         <v>32</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E39" s="1">
         <v>32</v>
@@ -2253,13 +2255,13 @@
         <v>44</v>
       </c>
       <c r="I39" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J39" s="6" t="s">
+      <c r="K39" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:11">
@@ -2267,7 +2269,7 @@
         <v>33</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E40" s="1">
         <v>33</v>
@@ -2282,13 +2284,13 @@
         <v>44</v>
       </c>
       <c r="I40" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="K40" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:11">
@@ -2296,7 +2298,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E41" s="1">
         <v>34</v>
@@ -2311,13 +2313,13 @@
         <v>44</v>
       </c>
       <c r="I41" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J41" s="6" t="s">
+      <c r="K41" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:11">
@@ -2325,7 +2327,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E42" s="1">
         <v>35</v>
@@ -2340,13 +2342,13 @@
         <v>44</v>
       </c>
       <c r="I42" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J42" s="6" t="s">
+      <c r="K42" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:11">
@@ -2354,7 +2356,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" s="1">
         <v>36</v>
@@ -2369,13 +2371,13 @@
         <v>44</v>
       </c>
       <c r="I43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J43" s="6" t="s">
+      <c r="K43" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ShengxiaoConfig.xlsx
+++ b/Excel/ShengxiaoConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="58">
   <si>
     <t>ID</t>
   </si>
@@ -182,6 +182,9 @@
   </si>
   <si>
     <t>太阴星</t>
+  </si>
+  <si>
+    <t>天府星</t>
   </si>
   <si>
     <t>武曲星</t>
@@ -2153,7 +2156,7 @@
         <v>29</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E36" s="1">
         <v>29</v>
@@ -2182,7 +2185,7 @@
         <v>30</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E37" s="1">
         <v>30</v>
@@ -2211,7 +2214,7 @@
         <v>31</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E38" s="1">
         <v>31</v>
@@ -2240,7 +2243,7 @@
         <v>32</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E39" s="1">
         <v>32</v>
@@ -2269,7 +2272,7 @@
         <v>33</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E40" s="1">
         <v>33</v>
@@ -2298,7 +2301,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E41" s="1">
         <v>34</v>
@@ -2327,7 +2330,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E42" s="1">
         <v>35</v>
@@ -2356,7 +2359,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E43" s="1">
         <v>36</v>
